--- a/week-01/Sweet cafe(1-9) (2)survey results.xlsx
+++ b/week-01/Sweet cafe(1-9) (2)survey results.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="26" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -205,7 +205,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -236,11 +236,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -306,16 +305,16 @@
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="mm/dd/yy;@"/>
+      <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2059,6 +2058,232 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="22"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="23"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="24"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="25"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="26"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="27"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="28"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="29"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="30"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="31"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="32"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="33"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="34"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -2092,6 +2317,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2107,6 +2337,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -2122,6 +2357,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2189,6 +2429,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2204,6 +2449,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -2219,6 +2469,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2283,6 +2538,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2298,6 +2558,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -2313,6 +2578,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2380,6 +2650,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -2395,6 +2670,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -2410,6 +2690,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-ADEA-4900-8833-0CF9CF4EB35C}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -3759,10 +4044,10 @@
         <n v="9"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Start time" numFmtId="168">
+    <cacheField name="Start time" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-08T05:58:03" maxDate="2026-04-09T11:43:24"/>
     </cacheField>
-    <cacheField name="Completion time" numFmtId="168">
+    <cacheField name="Completion time" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-08T05:58:32" maxDate="2026-04-09T11:43:37"/>
     </cacheField>
     <cacheField name="Time to complete" numFmtId="45">
@@ -4140,12 +4425,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A88BD282-1308-400F-B1C1-F1CC33145098}" name="PivotTable6" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A88BD282-1308-400F-B1C1-F1CC33145098}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="168" showAll="0"/>
-    <pivotField numFmtId="168" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="45" showAll="0">
       <items count="10">
         <item x="4"/>
@@ -4395,7 +4680,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81B67247-E7E3-4381-9222-B16EB8F12BB8}" name="PivotTable7" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81B67247-E7E3-4381-9222-B16EB8F12BB8}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:F8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="15">
     <pivotField dataField="1" showAll="0">
@@ -4412,8 +4697,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="168" showAll="0"/>
-    <pivotField numFmtId="168" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="45" showAll="0">
       <items count="10">
         <item x="4"/>
@@ -5066,7 +5351,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B3" t="s">
@@ -5074,34 +5359,34 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>9</v>
       </c>
     </row>
@@ -5127,7 +5412,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B1" t="s">
@@ -5135,15 +5420,15 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B4" t="s">
@@ -5163,70 +5448,64 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>8</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2">
+      <c r="F5">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>7</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>9</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2">
+      <c r="F7">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>16</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
         <v>8</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>16</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>5</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8">
         <v>45</v>
       </c>
     </row>
@@ -5241,8 +5520,7 @@
   <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
     <col min="5" max="12" width="20" bestFit="1" customWidth="1"/>
   </cols>
@@ -5251,13 +5529,13 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>45</v>
       </c>
       <c r="E1" t="s">
@@ -5289,13 +5567,13 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>46120.248645833301</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>46120.248981481498</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <f t="shared" ref="D2:D10" si="0">C2-B2</f>
         <v>3.3564819750608876E-4</v>
       </c>
@@ -5326,13 +5604,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>46120.2863194444</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>46120.286481481497</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <f t="shared" si="0"/>
         <v>1.6203709674300626E-4</v>
       </c>
@@ -5363,13 +5641,13 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="2">
         <v>46120.438541666699</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>46120.438854166699</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <f t="shared" si="0"/>
         <v>3.125000002910383E-4</v>
       </c>
@@ -5400,13 +5678,13 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>46120.448252314804</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>46120.448807870402</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <f t="shared" si="0"/>
         <v>5.555555981118232E-4</v>
       </c>
@@ -5437,13 +5715,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>46120.488599536999</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>46120.488726851901</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>1.2731490278383717E-4</v>
       </c>
@@ -5474,13 +5752,13 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>46120.488263888903</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>46120.488900463002</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>6.3657409918960184E-4</v>
       </c>
@@ -5511,13 +5789,13 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>46121.356053240699</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>46121.363206018497</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <f t="shared" si="0"/>
         <v>7.1527777981827967E-3</v>
       </c>
@@ -5548,13 +5826,13 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>46121.365983796299</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>46121.370162036997</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <f t="shared" si="0"/>
         <v>4.1782406988204457E-3</v>
       </c>
@@ -5585,13 +5863,13 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>46121.488472222198</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>46121.488622685203</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>1.5046300541143864E-4</v>
       </c>
@@ -5619,24 +5897,16 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3">
         <f>AVERAGE(D2:D10)</f>
         <v>1.5123457107822308E-3</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B12" s="3"/>
+      <c r="B12" s="2"/>
       <c r="J12">
         <f>SUM(COUNTIF(J2:J10,"Very likely"),COUNTIF(J2:J10,"Somewhat likely"))</f>
         <v>7</v>
@@ -5652,23 +5922,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b275f972-a0ec-44ed-acfc-93b347ca42d1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006BAB7F1D75092C43A80735B994755528" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b22aff8fbc88cc9afa746eced27ee7f9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b275f972-a0ec-44ed-acfc-93b347ca42d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0bd8c01aa11a802dfa259021a2182590" ns3:_="">
     <xsd:import namespace="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
@@ -5850,31 +6103,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1EC4132-BAB4-4567-8F8D-6F5B3D8A9571}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D41BA7-3873-4FE1-B1DC-FE0A098ADCB3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b275f972-a0ec-44ed-acfc-93b347ca42d1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A93F9229-4852-47BD-84B6-FFCC4F9C5BCE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5890,4 +6136,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6D41BA7-3873-4FE1-B1DC-FE0A098ADCB3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1EC4132-BAB4-4567-8F8D-6F5B3D8A9571}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>